--- a/fastApiProject/app/templates/平台内的经营者和从业人员收入信息报送表02.xlsx
+++ b/fastApiProject/app/templates/平台内的经营者和从业人员收入信息报送表02.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t>平台内的经营者和从业人员收入信息报送表</t>
   </si>
@@ -85,6 +85,12 @@
   </si>
   <si>
     <t>交易（订单）数量（笔）</t>
+  </si>
+  <si>
+    <t>个税</t>
+  </si>
+  <si>
+    <t>含税总额</t>
   </si>
   <si>
     <t>名称（姓名）</t>
@@ -935,7 +941,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1010,6 +1016,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1539,7 +1548,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AG8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="4" max="4" width="12.625" customWidth="1"/>
@@ -1695,7 +1704,7 @@
       </c>
       <c r="AE4" s="4"/>
     </row>
-    <row r="5" ht="14.25" spans="1:31">
+    <row r="5" ht="14.25" spans="1:33">
       <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
@@ -1751,54 +1760,60 @@
       <c r="AE5" s="7" t="s">
         <v>18</v>
       </c>
+      <c r="AF5" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG5" s="25" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="6" ht="14.25" spans="1:31">
+    <row r="6" ht="14.25" spans="1:33">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
       <c r="O6" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
       <c r="U6" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
@@ -1808,8 +1823,10 @@
       <c r="AC6" s="7"/>
       <c r="AD6" s="7"/>
       <c r="AE6" s="7"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="25"/>
     </row>
-    <row r="7" ht="14.25" spans="1:31">
+    <row r="7" ht="14.25" spans="1:33">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="13"/>
@@ -1822,49 +1839,51 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="O7" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="P7" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="R7" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="S7" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
       <c r="W7" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y7" s="8"/>
       <c r="Z7" s="8"/>
       <c r="AA7" s="8"/>
-      <c r="AB7" s="25"/>
+      <c r="AB7" s="26"/>
       <c r="AC7" s="7"/>
       <c r="AD7" s="7"/>
       <c r="AE7" s="7"/>
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="25"/>
     </row>
-    <row r="8" ht="28.5" spans="1:31">
+    <row r="8" ht="28.5" spans="1:33">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="16"/>
@@ -1889,26 +1908,28 @@
       <c r="V8" s="7"/>
       <c r="W8" s="7"/>
       <c r="X8" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AA8" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB8" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AC8" s="7"/>
       <c r="AD8" s="7"/>
       <c r="AE8" s="7"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="41">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:AE2"/>
     <mergeCell ref="J3:L3"/>
@@ -1948,6 +1969,8 @@
     <mergeCell ref="AC5:AC8"/>
     <mergeCell ref="AD5:AD8"/>
     <mergeCell ref="AE5:AE8"/>
+    <mergeCell ref="AF5:AF8"/>
+    <mergeCell ref="AG5:AG8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
